--- a/data/employees/EMP095/AST-EMP095-06.xlsx
+++ b/data/employees/EMP095/AST-EMP095-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Data Log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,184 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Experiment Data Log - Casey Lee (R&amp;D)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Casey Lee | Role: Director | Location: Bengaluru | Date: 2025-04-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp095 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>73</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp095 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>86</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Experiment ID</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Hypothesis</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Outcome</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Confidence</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Next Steps</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp095 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>70</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EXP-2026-041</t>
+          <t>EMP095</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Low-temp deposition</t>
+          <t>Ast Emp095 06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>2026-W04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.87</v>
+        <v>79</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>IP disclosure</t>
+          <t>Section 1: Data quality remediation. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EXP-2026-042</t>
+          <t>EMP095</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Novel etchant blend</t>
+          <t>Ast Emp095 06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>2026-W05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>72</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Continue</t>
+          <t>Section 1: Quarterly delivery milestones. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EXP-2026-043</t>
+          <t>EMP095</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Surface treatment A</t>
+          <t>Ast Emp095 06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>2026-W06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Inconclusive</t>
+          <t>Velocity</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.51</v>
+        <v>68</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Redesign</t>
+          <t>Section 1: Data quality remediation. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EXP-2026-044</t>
+          <t>EMP095</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Plasma optimisation</t>
+          <t>Ast Emp095 06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>2026-W07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>69</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Start Q3</t>
+          <t>Section 1: Fabric semantic model planning. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp095 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>78</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp095 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>89</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp095 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>84</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp095 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>69</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp095 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>61</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp095 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>64</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp095 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>87</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp095 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>99</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp095 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>83</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp095 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>75</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp095 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>78</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp095 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>63</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp095 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>73</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp095 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>83</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp095 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>91</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp095 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>97</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp095 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>96</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP095</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP095 contributes to ast emp095 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>